--- a/artfynd/S 4125-2022 artfynd.xlsx
+++ b/artfynd/S 4125-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,113 +1855,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>134519514</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Storflon, Storflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>461751</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7173757</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4125-2022 artfynd.xlsx
+++ b/artfynd/S 4125-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,6 +1855,113 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134519514</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storflon, Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>461751</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7173757</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4125-2022 artfynd.xlsx
+++ b/artfynd/S 4125-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225417</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225419</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225414</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225413</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225416</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225418</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1505,6 +1540,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225420</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1624,6 +1664,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225421</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,6 +1766,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134519416</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1854,6 +1904,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225415</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1961,8 +2016,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134519514</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 4125-2022 artfynd.xlsx
+++ b/artfynd/S 4125-2022 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>134519514</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
